--- a/04-da-v8-user-journey/13-KahootQuizTemplate.xlsx
+++ b/04-da-v8-user-journey/13-KahootQuizTemplate.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">Quiz template</t>
   </si>
@@ -58,72 +58,61 @@
     <t xml:space="preserve">Correct answer(s) - choose at least one</t>
   </si>
   <si>
-    <t xml:space="preserve">Muestra las ventas totales por tienda</t>
+    <t xml:space="preserve">Cuando reducimos el abandono entre dos etapas del funnel, ¿qué estamos simulando?</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT SUM(amount) FROM payment GROUP BY store_id</t>
+    <t xml:space="preserve">Una mejora en la conversión entre esas etapas</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT store_id FROM payment</t>
+    <t xml:space="preserve">Un aumento en el ARPU</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM payment ORDER BY store_id</t>
+    <t xml:space="preserve">Una segmentación de usuarios</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT store_id</t>
+    <t xml:space="preserve">Una prueba A/B entre canales</t>
   </si>
   <si>
-    <t xml:space="preserve">Muestra las categorías con más de 20 películas</t>
+    <t xml:space="preserve">¿Por qué mantenemos las tasas históricas al propagar una mejora en una simulación?</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT category_id FROM film HAVING COUNT(*)&gt;20</t>
+    <t xml:space="preserve">Para que los resultados sean más realistas</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT category_id</t>
+    <t xml:space="preserve">Porque así se incrementan todas las etapas por igual</t>
   </si>
   <si>
-    <t xml:space="preserve"> COUNT(*) FROM film GROUP BY category_id HAVING COUNT(*)&gt;20</t>
+    <t xml:space="preserve">Para evitar usar CTEs en SQL</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM film WHERE COUNT(*)&gt;20</t>
+    <t xml:space="preserve">Para simular escenarios aleatorios</t>
   </si>
   <si>
-    <t xml:space="preserve">Muestra los clientes con más de 10 rentas</t>
+    <t xml:space="preserve">Si una fuente de tráfico genera menos usuarios pero mayor ingreso promedio, ¿qué se debe priorizar?</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT customer_id FROM rental HAVING COUNT(*)&gt;10</t>
+    <t xml:space="preserve">Priorizar la fuente con mayor revenue impact</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT * FROM rental ORDER BY COUNT(*)&gt;10</t>
+    <t xml:space="preserve">Aumentar el tráfico en todas las fuentes</t>
   </si>
   <si>
-    <t xml:space="preserve">SELECT customer_id</t>
+    <t xml:space="preserve">Invertir en la fuente con más usuarios</t>
   </si>
   <si>
-    <t xml:space="preserve"> COUNT(*) FROM rental GROUP BY customer_id HAVING COUNT(*)&gt;10</t>
+    <t xml:space="preserve">Reducir el ARPU de la fuente menos rentable</t>
   </si>
   <si>
-    <t xml:space="preserve">Muestra las 5 categorías más rentables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT * FROM category LIMIT 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT name</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> SUM(amount) FROM payment GROUP BY name ORDER BY SUM(amount) DESC LIMIT 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT SUM(amount) FROM payment LIMIT 5</t>
+    <t xml:space="preserve">El ARPU sirve únicamente para medir la cantidad de usuarios activos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="&quot;VERDADERO&quot;;&quot;VERDADERO&quot;;&quot;FALSO&quot;"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -294,7 +283,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -361,6 +350,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -488,9 +481,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>340200</xdr:colOff>
+      <xdr:colOff>339840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>304200</xdr:rowOff>
+      <xdr:rowOff>303840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -500,7 +493,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="908280" y="228960"/>
-          <a:ext cx="313200" cy="313200"/>
+          <a:ext cx="312840" cy="312840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -528,9 +521,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>340200</xdr:colOff>
+      <xdr:colOff>339840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>304200</xdr:rowOff>
+      <xdr:rowOff>303840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -540,7 +533,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="908280" y="228960"/>
-          <a:ext cx="313200" cy="313200"/>
+          <a:ext cx="312840" cy="312840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -568,9 +561,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1302480</xdr:colOff>
+      <xdr:colOff>1302120</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>418680</xdr:rowOff>
+      <xdr:rowOff>418320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -584,7 +577,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="927360" y="228960"/>
-          <a:ext cx="1256400" cy="427680"/>
+          <a:ext cx="1256040" cy="427320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -777,7 +770,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA1001"/>
+  <dimension ref="A1:AA1048576"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.5"/>
@@ -1046,9 +1039,9 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="30.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>12</v>
@@ -1069,7 +1062,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1093,7 +1086,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>17</v>
@@ -1138,7 +1131,7 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>22</v>
@@ -1159,7 +1152,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -1183,28 +1176,24 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>31</v>
-      </c>
+      <c r="C12" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="15" t="n">
         <v>20</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1228,7 +1217,7 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1259,7 +1248,7 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -1290,7 +1279,7 @@
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -1321,7 +1310,7 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -1352,7 +1341,7 @@
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -1383,7 +1372,7 @@
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -1414,7 +1403,7 @@
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -1443,17 +1432,17 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+        <v>21</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1474,17 +1463,17 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1505,17 +1494,17 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1536,17 +1525,17 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
       <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="19"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -1567,17 +1556,17 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+        <v>25</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
+      <c r="H24" s="19"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1598,17 +1587,17 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="19"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1629,17 +1618,17 @@
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
     </row>
-    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1660,17 +1649,17 @@
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
     </row>
-    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1691,17 +1680,17 @@
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
+      <c r="H28" s="20"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1724,15 +1713,15 @@
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="18"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -1755,15 +1744,15 @@
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+        <v>31</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="18"/>
+      <c r="H30" s="20"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -1786,15 +1775,15 @@
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+        <v>32</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
       <c r="G31" s="15"/>
-      <c r="H31" s="18"/>
+      <c r="H31" s="20"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1817,15 +1806,15 @@
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
       <c r="G32" s="15"/>
-      <c r="H32" s="18"/>
+      <c r="H32" s="20"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -1848,15 +1837,15 @@
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
       <c r="G33" s="15"/>
-      <c r="H33" s="18"/>
+      <c r="H33" s="20"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -1879,15 +1868,15 @@
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="15"/>
-      <c r="H34" s="18"/>
+      <c r="H34" s="20"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -1910,15 +1899,15 @@
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="15"/>
-      <c r="H35" s="18"/>
+      <c r="H35" s="20"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -1941,15 +1930,15 @@
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="15"/>
-      <c r="H36" s="18"/>
+      <c r="H36" s="20"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -1972,15 +1961,15 @@
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
+        <v>38</v>
+      </c>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="15"/>
-      <c r="H37" s="19"/>
+      <c r="H37" s="20"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2003,15 +1992,15 @@
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
+        <v>39</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
       <c r="G38" s="15"/>
-      <c r="H38" s="19"/>
+      <c r="H38" s="20"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -2034,15 +2023,15 @@
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="15"/>
-      <c r="H39" s="19"/>
+      <c r="H39" s="20"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -2065,15 +2054,15 @@
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
+        <v>41</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="15"/>
-      <c r="H40" s="19"/>
+      <c r="H40" s="20"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -2096,15 +2085,15 @@
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
+        <v>42</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="15"/>
-      <c r="H41" s="19"/>
+      <c r="H41" s="20"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -2127,15 +2116,15 @@
     </row>
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
+        <v>43</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="15"/>
-      <c r="H42" s="19"/>
+      <c r="H42" s="20"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2158,15 +2147,15 @@
     </row>
     <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
+        <v>44</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
       <c r="G43" s="15"/>
-      <c r="H43" s="19"/>
+      <c r="H43" s="20"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -2189,15 +2178,15 @@
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
       <c r="G44" s="15"/>
-      <c r="H44" s="19"/>
+      <c r="H44" s="20"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -2220,15 +2209,15 @@
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
       <c r="G45" s="15"/>
-      <c r="H45" s="19"/>
+      <c r="H45" s="20"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -2251,15 +2240,15 @@
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
+        <v>47</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
       <c r="G46" s="15"/>
-      <c r="H46" s="19"/>
+      <c r="H46" s="20"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -2282,15 +2271,15 @@
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
+        <v>48</v>
+      </c>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
       <c r="G47" s="15"/>
-      <c r="H47" s="19"/>
+      <c r="H47" s="20"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -2313,15 +2302,15 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
+        <v>49</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
       <c r="G48" s="15"/>
-      <c r="H48" s="19"/>
+      <c r="H48" s="20"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -2344,15 +2333,15 @@
     </row>
     <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="15"/>
-      <c r="H49" s="19"/>
+      <c r="H49" s="20"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -2375,15 +2364,15 @@
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
       <c r="G50" s="15"/>
-      <c r="H50" s="19"/>
+      <c r="H50" s="20"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -2406,15 +2395,15 @@
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
+        <v>52</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="15"/>
-      <c r="H51" s="19"/>
+      <c r="H51" s="20"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -2437,15 +2426,15 @@
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
+        <v>53</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
       <c r="G52" s="15"/>
-      <c r="H52" s="19"/>
+      <c r="H52" s="20"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -2468,15 +2457,15 @@
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
+        <v>54</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
       <c r="G53" s="15"/>
-      <c r="H53" s="19"/>
+      <c r="H53" s="20"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -2499,15 +2488,15 @@
     </row>
     <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
+        <v>55</v>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
       <c r="G54" s="15"/>
-      <c r="H54" s="19"/>
+      <c r="H54" s="20"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -2530,15 +2519,15 @@
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
+        <v>56</v>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
       <c r="G55" s="15"/>
-      <c r="H55" s="19"/>
+      <c r="H55" s="20"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -2561,15 +2550,15 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
+        <v>57</v>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
       <c r="G56" s="15"/>
-      <c r="H56" s="19"/>
+      <c r="H56" s="20"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -2592,15 +2581,15 @@
     </row>
     <row r="57" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
+        <v>58</v>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
       <c r="G57" s="15"/>
-      <c r="H57" s="19"/>
+      <c r="H57" s="20"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -2623,15 +2612,15 @@
     </row>
     <row r="58" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
+        <v>59</v>
+      </c>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
       <c r="G58" s="15"/>
-      <c r="H58" s="19"/>
+      <c r="H58" s="20"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -2654,15 +2643,15 @@
     </row>
     <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
       <c r="G59" s="15"/>
-      <c r="H59" s="19"/>
+      <c r="H59" s="20"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -2685,15 +2674,15 @@
     </row>
     <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
+        <v>61</v>
+      </c>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
       <c r="G60" s="15"/>
-      <c r="H60" s="19"/>
+      <c r="H60" s="20"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -2716,15 +2705,15 @@
     </row>
     <row r="61" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
+        <v>62</v>
+      </c>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
       <c r="G61" s="15"/>
-      <c r="H61" s="19"/>
+      <c r="H61" s="20"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -2747,15 +2736,15 @@
     </row>
     <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
+        <v>63</v>
+      </c>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
       <c r="G62" s="15"/>
-      <c r="H62" s="19"/>
+      <c r="H62" s="20"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -2778,15 +2767,15 @@
     </row>
     <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
+        <v>64</v>
+      </c>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
       <c r="G63" s="15"/>
-      <c r="H63" s="19"/>
+      <c r="H63" s="20"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -2809,15 +2798,15 @@
     </row>
     <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
+        <v>65</v>
+      </c>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
       <c r="G64" s="15"/>
-      <c r="H64" s="19"/>
+      <c r="H64" s="20"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -2840,15 +2829,15 @@
     </row>
     <row r="65" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
+        <v>66</v>
+      </c>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
       <c r="G65" s="15"/>
-      <c r="H65" s="19"/>
+      <c r="H65" s="20"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
@@ -2871,15 +2860,15 @@
     </row>
     <row r="66" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
+        <v>67</v>
+      </c>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
       <c r="G66" s="15"/>
-      <c r="H66" s="19"/>
+      <c r="H66" s="20"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -2902,15 +2891,15 @@
     </row>
     <row r="67" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
+        <v>68</v>
+      </c>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
       <c r="G67" s="15"/>
-      <c r="H67" s="19"/>
+      <c r="H67" s="20"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -2933,15 +2922,15 @@
     </row>
     <row r="68" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
+        <v>69</v>
+      </c>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
       <c r="G68" s="15"/>
-      <c r="H68" s="19"/>
+      <c r="H68" s="20"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
@@ -2964,15 +2953,15 @@
     </row>
     <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
       <c r="G69" s="15"/>
-      <c r="H69" s="19"/>
+      <c r="H69" s="20"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -2995,15 +2984,15 @@
     </row>
     <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
       <c r="G70" s="15"/>
-      <c r="H70" s="19"/>
+      <c r="H70" s="20"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -3026,15 +3015,15 @@
     </row>
     <row r="71" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
+        <v>72</v>
+      </c>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
       <c r="G71" s="15"/>
-      <c r="H71" s="19"/>
+      <c r="H71" s="20"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -3057,15 +3046,15 @@
     </row>
     <row r="72" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
+        <v>73</v>
+      </c>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
       <c r="G72" s="15"/>
-      <c r="H72" s="19"/>
+      <c r="H72" s="20"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -3088,15 +3077,15 @@
     </row>
     <row r="73" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
+        <v>74</v>
+      </c>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
       <c r="G73" s="15"/>
-      <c r="H73" s="19"/>
+      <c r="H73" s="20"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
@@ -3119,15 +3108,15 @@
     </row>
     <row r="74" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
       <c r="G74" s="15"/>
-      <c r="H74" s="19"/>
+      <c r="H74" s="20"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
@@ -3150,15 +3139,15 @@
     </row>
     <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="17"/>
+        <v>76</v>
+      </c>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
       <c r="G75" s="15"/>
-      <c r="H75" s="19"/>
+      <c r="H75" s="20"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
@@ -3181,15 +3170,15 @@
     </row>
     <row r="76" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="17"/>
+        <v>77</v>
+      </c>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
       <c r="G76" s="15"/>
-      <c r="H76" s="19"/>
+      <c r="H76" s="20"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
@@ -3212,15 +3201,15 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
+        <v>78</v>
+      </c>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
       <c r="G77" s="15"/>
-      <c r="H77" s="19"/>
+      <c r="H77" s="20"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
@@ -3243,15 +3232,15 @@
     </row>
     <row r="78" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
       <c r="G78" s="15"/>
-      <c r="H78" s="19"/>
+      <c r="H78" s="20"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
@@ -3274,15 +3263,15 @@
     </row>
     <row r="79" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
       <c r="G79" s="15"/>
-      <c r="H79" s="19"/>
+      <c r="H79" s="20"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
@@ -3305,15 +3294,15 @@
     </row>
     <row r="80" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
+        <v>81</v>
+      </c>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
       <c r="G80" s="15"/>
-      <c r="H80" s="19"/>
+      <c r="H80" s="20"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -3336,15 +3325,15 @@
     </row>
     <row r="81" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
       <c r="G81" s="15"/>
-      <c r="H81" s="19"/>
+      <c r="H81" s="20"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
@@ -3367,15 +3356,15 @@
     </row>
     <row r="82" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
+        <v>83</v>
+      </c>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
       <c r="G82" s="15"/>
-      <c r="H82" s="19"/>
+      <c r="H82" s="20"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
@@ -3398,15 +3387,15 @@
     </row>
     <row r="83" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17"/>
+        <v>84</v>
+      </c>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
       <c r="G83" s="15"/>
-      <c r="H83" s="19"/>
+      <c r="H83" s="20"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -3429,15 +3418,15 @@
     </row>
     <row r="84" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
       <c r="G84" s="15"/>
-      <c r="H84" s="19"/>
+      <c r="H84" s="20"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
@@ -3460,15 +3449,15 @@
     </row>
     <row r="85" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="17"/>
+        <v>86</v>
+      </c>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
       <c r="G85" s="15"/>
-      <c r="H85" s="19"/>
+      <c r="H85" s="20"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
@@ -3491,15 +3480,15 @@
     </row>
     <row r="86" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="17"/>
+        <v>87</v>
+      </c>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
       <c r="G86" s="15"/>
-      <c r="H86" s="19"/>
+      <c r="H86" s="20"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
@@ -3522,15 +3511,15 @@
     </row>
     <row r="87" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
+        <v>88</v>
+      </c>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
       <c r="G87" s="15"/>
-      <c r="H87" s="19"/>
+      <c r="H87" s="20"/>
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
@@ -3553,15 +3542,15 @@
     </row>
     <row r="88" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="17"/>
+        <v>89</v>
+      </c>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
       <c r="G88" s="15"/>
-      <c r="H88" s="19"/>
+      <c r="H88" s="20"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
@@ -3584,15 +3573,15 @@
     </row>
     <row r="89" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
       <c r="G89" s="15"/>
-      <c r="H89" s="19"/>
+      <c r="H89" s="20"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
@@ -3615,15 +3604,15 @@
     </row>
     <row r="90" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="17"/>
-      <c r="F90" s="17"/>
+        <v>91</v>
+      </c>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18"/>
       <c r="G90" s="15"/>
-      <c r="H90" s="19"/>
+      <c r="H90" s="20"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
@@ -3646,15 +3635,15 @@
     </row>
     <row r="91" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="17"/>
-      <c r="F91" s="17"/>
+        <v>92</v>
+      </c>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
       <c r="G91" s="15"/>
-      <c r="H91" s="19"/>
+      <c r="H91" s="20"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
@@ -3677,15 +3666,15 @@
     </row>
     <row r="92" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="17"/>
+        <v>93</v>
+      </c>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
       <c r="G92" s="15"/>
-      <c r="H92" s="19"/>
+      <c r="H92" s="20"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
@@ -3708,15 +3697,15 @@
     </row>
     <row r="93" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="17"/>
-      <c r="F93" s="17"/>
+        <v>94</v>
+      </c>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
       <c r="G93" s="15"/>
-      <c r="H93" s="19"/>
+      <c r="H93" s="20"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
@@ -3739,15 +3728,15 @@
     </row>
     <row r="94" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="17"/>
+        <v>95</v>
+      </c>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
       <c r="G94" s="15"/>
-      <c r="H94" s="19"/>
+      <c r="H94" s="20"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
@@ -3770,15 +3759,15 @@
     </row>
     <row r="95" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="17"/>
+        <v>96</v>
+      </c>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
       <c r="G95" s="15"/>
-      <c r="H95" s="19"/>
+      <c r="H95" s="20"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
@@ -3801,15 +3790,15 @@
     </row>
     <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="17"/>
-      <c r="F96" s="17"/>
+        <v>97</v>
+      </c>
+      <c r="B96" s="18"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="18"/>
       <c r="G96" s="15"/>
-      <c r="H96" s="19"/>
+      <c r="H96" s="20"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
@@ -3832,15 +3821,15 @@
     </row>
     <row r="97" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="17"/>
+        <v>98</v>
+      </c>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
       <c r="G97" s="15"/>
-      <c r="H97" s="19"/>
+      <c r="H97" s="20"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
@@ -3863,15 +3852,15 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
-      <c r="D98" s="17"/>
-      <c r="E98" s="17"/>
-      <c r="F98" s="17"/>
+        <v>99</v>
+      </c>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
       <c r="G98" s="15"/>
-      <c r="H98" s="19"/>
+      <c r="H98" s="20"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
@@ -3894,15 +3883,15 @@
     </row>
     <row r="99" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="17"/>
-      <c r="F99" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="B99" s="18"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="18"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
       <c r="G99" s="15"/>
-      <c r="H99" s="19"/>
+      <c r="H99" s="20"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
@@ -3923,285 +3912,15 @@
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
     </row>
-    <row r="100" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="17"/>
-      <c r="F100" s="17"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" s="2"/>
-      <c r="Q100" s="2"/>
-      <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
-      <c r="T100" s="2"/>
-      <c r="U100" s="2"/>
-      <c r="V100" s="2"/>
-      <c r="W100" s="2"/>
-      <c r="X100" s="2"/>
-      <c r="Y100" s="2"/>
-      <c r="Z100" s="2"/>
-      <c r="AA100" s="2"/>
-    </row>
-    <row r="101" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="B101" s="17"/>
-      <c r="C101" s="17"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="17"/>
-      <c r="F101" s="17"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" s="2"/>
-      <c r="Q101" s="2"/>
-      <c r="R101" s="2"/>
-      <c r="S101" s="2"/>
-      <c r="T101" s="2"/>
-      <c r="U101" s="2"/>
-      <c r="V101" s="2"/>
-      <c r="W101" s="2"/>
-      <c r="X101" s="2"/>
-      <c r="Y101" s="2"/>
-      <c r="Z101" s="2"/>
-      <c r="AA101" s="2"/>
-    </row>
-    <row r="102" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="17"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="19"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" s="2"/>
-      <c r="Q102" s="2"/>
-      <c r="R102" s="2"/>
-      <c r="S102" s="2"/>
-      <c r="T102" s="2"/>
-      <c r="U102" s="2"/>
-      <c r="V102" s="2"/>
-      <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
-      <c r="Y102" s="2"/>
-      <c r="Z102" s="2"/>
-      <c r="AA102" s="2"/>
-    </row>
-    <row r="103" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="B103" s="17"/>
-      <c r="C103" s="17"/>
-      <c r="D103" s="17"/>
-      <c r="E103" s="17"/>
-      <c r="F103" s="17"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" s="2"/>
-      <c r="Q103" s="2"/>
-      <c r="R103" s="2"/>
-      <c r="S103" s="2"/>
-      <c r="T103" s="2"/>
-      <c r="U103" s="2"/>
-      <c r="V103" s="2"/>
-      <c r="W103" s="2"/>
-      <c r="X103" s="2"/>
-      <c r="Y103" s="2"/>
-      <c r="Z103" s="2"/>
-      <c r="AA103" s="2"/>
-    </row>
-    <row r="104" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="B104" s="17"/>
-      <c r="C104" s="17"/>
-      <c r="D104" s="17"/>
-      <c r="E104" s="17"/>
-      <c r="F104" s="17"/>
-      <c r="G104" s="15"/>
-      <c r="H104" s="19"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" s="2"/>
-      <c r="Q104" s="2"/>
-      <c r="R104" s="2"/>
-      <c r="S104" s="2"/>
-      <c r="T104" s="2"/>
-      <c r="U104" s="2"/>
-      <c r="V104" s="2"/>
-      <c r="W104" s="2"/>
-      <c r="X104" s="2"/>
-      <c r="Y104" s="2"/>
-      <c r="Z104" s="2"/>
-      <c r="AA104" s="2"/>
-    </row>
-    <row r="105" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="B105" s="17"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="17"/>
-      <c r="E105" s="17"/>
-      <c r="F105" s="17"/>
-      <c r="G105" s="15"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" s="2"/>
-      <c r="Q105" s="2"/>
-      <c r="R105" s="2"/>
-      <c r="S105" s="2"/>
-      <c r="T105" s="2"/>
-      <c r="U105" s="2"/>
-      <c r="V105" s="2"/>
-      <c r="W105" s="2"/>
-      <c r="X105" s="2"/>
-      <c r="Y105" s="2"/>
-      <c r="Z105" s="2"/>
-      <c r="AA105" s="2"/>
-    </row>
-    <row r="106" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="B106" s="17"/>
-      <c r="C106" s="17"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="17"/>
-      <c r="G106" s="15"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" s="2"/>
-      <c r="Q106" s="2"/>
-      <c r="R106" s="2"/>
-      <c r="S106" s="2"/>
-      <c r="T106" s="2"/>
-      <c r="U106" s="2"/>
-      <c r="V106" s="2"/>
-      <c r="W106" s="2"/>
-      <c r="X106" s="2"/>
-      <c r="Y106" s="2"/>
-      <c r="Z106" s="2"/>
-      <c r="AA106" s="2"/>
-    </row>
-    <row r="107" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="B107" s="17"/>
-      <c r="C107" s="17"/>
-      <c r="D107" s="17"/>
-      <c r="E107" s="17"/>
-      <c r="F107" s="17"/>
-      <c r="G107" s="15"/>
-      <c r="H107" s="19"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" s="2"/>
-      <c r="Q107" s="2"/>
-      <c r="R107" s="2"/>
-      <c r="S107" s="2"/>
-      <c r="T107" s="2"/>
-      <c r="U107" s="2"/>
-      <c r="V107" s="2"/>
-      <c r="W107" s="2"/>
-      <c r="X107" s="2"/>
-      <c r="Y107" s="2"/>
-      <c r="Z107" s="2"/>
-      <c r="AA107" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="B108" s="17"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="17"/>
-      <c r="E108" s="17"/>
-      <c r="F108" s="17"/>
-      <c r="G108" s="15"/>
-      <c r="H108" s="19"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" s="2"/>
-      <c r="Q108" s="2"/>
-      <c r="R108" s="2"/>
-      <c r="S108" s="2"/>
-      <c r="T108" s="2"/>
-      <c r="U108" s="2"/>
-      <c r="V108" s="2"/>
-      <c r="W108" s="2"/>
-      <c r="X108" s="2"/>
-      <c r="Y108" s="2"/>
-      <c r="Z108" s="2"/>
-      <c r="AA108" s="2"/>
-    </row>
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4966,39 +4685,29 @@
     <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B6:H6"/>
   </mergeCells>
-  <conditionalFormatting sqref="C14:F18 B9:B108 C9:F9">
+  <conditionalFormatting sqref="C9:F9 B9:B99">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEN(B9)&gt;120</formula>
+      <formula>LEN(#REF!)&gt;120</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:F108 C9:F12">
+  <conditionalFormatting sqref="C9:F99">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEN(C9)&gt;75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B13">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEN(B10)&gt;120</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:F13">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEN(C13)&gt;75</formula>
+      <formula>LEN(#REF!)&gt;75</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
